--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.76341326668577</v>
+        <v>10.52405465583644</v>
       </c>
       <c r="D2" t="n">
-        <v>34.52361153017482</v>
+        <v>5.610086873653408</v>
       </c>
       <c r="E2" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F2" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.7711398206817</v>
+        <v>10.36281022086078</v>
       </c>
       <c r="D3" t="n">
-        <v>44.63742824133129</v>
+        <v>7.253582089216335</v>
       </c>
       <c r="E3" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F3" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.27763321372429</v>
+        <v>9.470115397230199</v>
       </c>
       <c r="D4" t="n">
-        <v>45.96194077712559</v>
+        <v>7.468815376282909</v>
       </c>
       <c r="E4" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F4" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.68022310551908</v>
+        <v>5.148036254646851</v>
       </c>
       <c r="D5" t="n">
-        <v>20.86272341146068</v>
+        <v>3.39019255436236</v>
       </c>
       <c r="E5" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F5" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.18138035127755</v>
+        <v>8.479474307082601</v>
       </c>
       <c r="D6" t="n">
-        <v>52.53079939752207</v>
+        <v>8.536254902097337</v>
       </c>
       <c r="E6" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F6" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.88835423428677</v>
+        <v>3.394357563071601</v>
       </c>
       <c r="D7" t="n">
-        <v>21.20370777807886</v>
+        <v>3.445602513937815</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F7" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.221844892302082</v>
+        <v>1.336049794999088</v>
       </c>
       <c r="D8" t="n">
-        <v>8.651063118673825</v>
+        <v>1.405797756784497</v>
       </c>
       <c r="E8" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F8" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.94892863707163</v>
+        <v>8.60420090352414</v>
       </c>
       <c r="D9" t="n">
-        <v>53.13419609523722</v>
+        <v>8.634306865476049</v>
       </c>
       <c r="E9" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F9" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.84826291163222</v>
+        <v>3.875342723140236</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77792354150317</v>
+        <v>3.863912575494265</v>
       </c>
       <c r="E10" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F10" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.18223486397529</v>
+        <v>6.529613165395984</v>
       </c>
       <c r="D11" t="n">
-        <v>40.29714072685638</v>
+        <v>6.548285368114161</v>
       </c>
       <c r="E11" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F11" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.34383616986916</v>
+        <v>7.205873377603739</v>
       </c>
       <c r="D12" t="n">
-        <v>44.11001130888997</v>
+        <v>7.16787683769462</v>
       </c>
       <c r="E12" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F12" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41455817304791</v>
+        <v>3.804865703120286</v>
       </c>
       <c r="D13" t="n">
-        <v>23.02252513506885</v>
+        <v>3.741160334448688</v>
       </c>
       <c r="E13" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F13" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.30790099525026</v>
+        <v>5.900033911728167</v>
       </c>
       <c r="D14" t="n">
-        <v>35.95573624887854</v>
+        <v>5.842807140442764</v>
       </c>
       <c r="E14" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F14" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.51186597353487</v>
+        <v>7.720678220699416</v>
       </c>
       <c r="D15" t="n">
-        <v>47.09115602412506</v>
+        <v>7.652312853920321</v>
       </c>
       <c r="E15" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F15" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>48.63732604392309</v>
+        <v>7.903565482137502</v>
       </c>
       <c r="D16" t="n">
-        <v>48.34848314498837</v>
+        <v>7.85662851106061</v>
       </c>
       <c r="E16" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F16" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>61.22203838226439</v>
+        <v>9.948581237117965</v>
       </c>
       <c r="D17" t="n">
-        <v>61.00517906837898</v>
+        <v>9.913341598611584</v>
       </c>
       <c r="E17" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F17" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>44.97659213352085</v>
+        <v>7.308696221697137</v>
       </c>
       <c r="D18" t="n">
-        <v>44.14180069021494</v>
+        <v>7.173042612159927</v>
       </c>
       <c r="E18" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F18" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.25342986609477</v>
+        <v>6.7036823532404</v>
       </c>
       <c r="D19" t="n">
-        <v>40.42193685477753</v>
+        <v>6.568564738901348</v>
       </c>
       <c r="E19" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F19" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>71.07599782921353</v>
+        <v>11.5498496472472</v>
       </c>
       <c r="D20" t="n">
-        <v>70.34099691121753</v>
+        <v>11.43041199807285</v>
       </c>
       <c r="E20" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F20" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>59.79460057049837</v>
+        <v>9.716622592705985</v>
       </c>
       <c r="D21" t="n">
-        <v>58.95559390297335</v>
+        <v>9.58028400923317</v>
       </c>
       <c r="E21" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F21" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>67.06589147652797</v>
+        <v>10.89820736493579</v>
       </c>
       <c r="D22" t="n">
-        <v>66.26782890289522</v>
+        <v>10.76852219672047</v>
       </c>
       <c r="E22" t="n">
-        <v>16.65626290151922</v>
+        <v>2.706642721496873</v>
       </c>
       <c r="F22" t="n">
-        <v>15.66698345163512</v>
+        <v>2.545884810890707</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
